--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.81.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.81.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -823,7 +823,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.81.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.81.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -597,16 +597,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L43: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ã€�</t>
+          <t>L59: stray/suspicious non-ASCII glyph(s): U+4E34 CJK UNIFIED IDEOGRAPH-4E34 | isolated marker/symbol line :: 临</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE | isolated marker/symbol line :: â€˜</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]74</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]74</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L10: isolated marker/symbol line :: 74</t>
@@ -614,7 +618,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE | isolated marker/symbol line :: â€˜</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]74</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -641,7 +645,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -652,24 +656,20 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: follows:â€”</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L29: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: the Court when by any positive rules to refuse the motion to dismiss, onâ€˜</t>
-        </is>
-      </c>
+          <t>L86: stray/suspicious non-ASCII glyph(s): U+4ECA CJK UNIFIED IDEOGRAPH-4ECA | isolated marker/symbol line :: 今</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L43: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ã€�</t>
+          <t>L43: isolated marker/symbol line :: 、</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L52: isolated marker/symbol line :: a</t>
+          <t>L5: isolated marker/symbol line :: ‘</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -705,16 +705,8 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00B4 ACUTE ACCENT | isolated marker/symbol line :: ä¸´</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L39: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: follows:â€”</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -722,7 +714,11 @@
           <t>L58: isolated marker/symbol line :: V</t>
         </is>
       </c>
-      <c r="O4" s="1" t="inlineStr"/>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>L52: isolated marker/symbol line :: a</t>
+        </is>
+      </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr"/>
@@ -747,7 +743,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -762,7 +758,7 @@
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00B4 ACUTE ACCENT | isolated marker/symbol line :: ä¸´</t>
+          <t>L59: stray/suspicious non-ASCII glyph(s): U+4E34 CJK UNIFIED IDEOGRAPH-4E34 | isolated marker/symbol line :: 临</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr"/>
@@ -805,7 +801,7 @@
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L87: isolated marker/symbol line :: A</t>
+          <t>L86: stray/suspicious non-ASCII glyph(s): U+4ECA CJK UNIFIED IDEOGRAPH-4ECA | isolated marker/symbol line :: 今</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr"/>
@@ -848,7 +844,7 @@
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L88: symbol-only separator/garbage line :: 411).</t>
+          <t>L87: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr"/>
@@ -891,7 +887,7 @@
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L89: isolated marker/symbol line :: B</t>
+          <t>L88: symbol-only separator/garbage line :: 411).</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr"/>
@@ -934,7 +930,7 @@
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L106: symbol-only separator/garbage line :: 1850.</t>
+          <t>L89: isolated marker/symbol line :: B</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr"/>
@@ -957,12 +953,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -977,7 +973,7 @@
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L123: isolated marker/symbol line :: S</t>
+          <t>L106: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr"/>
@@ -1005,7 +1001,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1018,7 +1014,11 @@
       <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
-      <c r="N11" s="1" t="inlineStr"/>
+      <c r="N11" s="1" t="inlineStr">
+        <is>
+          <t>L123: isolated marker/symbol line :: S</t>
+        </is>
+      </c>
       <c r="O11" s="1" t="inlineStr"/>
       <c r="P11" s="1" t="inlineStr"/>
       <c r="Q11" s="1" t="inlineStr"/>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
